--- a/StableD/GRC2/generateRSSI_2025-02-13_12-51-49-redo0417/rssi_output.xlsx
+++ b/StableD/GRC2/generateRSSI_2025-02-13_12-51-49-redo0417/rssi_output.xlsx
@@ -2841,2410 +2841,2410 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="n">
-        <v>-28.43412399291992</v>
+        <v>-83.47545623779297</v>
       </c>
       <c r="B1" t="n">
-        <v>-33.54964447021484</v>
+        <v>-61.97690582275391</v>
       </c>
       <c r="C1" t="n">
-        <v>-34.85509490966797</v>
+        <v>-78.26573181152344</v>
       </c>
       <c r="D1" t="n">
-        <v>-35.84444427490234</v>
+        <v>-64.65229797363281</v>
       </c>
       <c r="E1" t="n">
-        <v>-38.98825836181641</v>
+        <v>-78.60665130615234</v>
       </c>
       <c r="F1" t="n">
-        <v>-41.96891784667969</v>
+        <v>-80.25131225585938</v>
       </c>
       <c r="G1" t="n">
-        <v>-48.98076248168945</v>
+        <v>-69.41667175292969</v>
       </c>
       <c r="H1" t="n">
-        <v>-46.20653533935547</v>
+        <v>-81.68679809570312</v>
       </c>
       <c r="I1" t="n">
-        <v>-49.98447036743164</v>
+        <v>-61.9062385559082</v>
       </c>
       <c r="J1" t="n">
-        <v>-43.8991813659668</v>
+        <v>-73.72789001464844</v>
       </c>
       <c r="K1" t="n">
-        <v>-50.33821105957031</v>
+        <v>-79.95742034912109</v>
       </c>
       <c r="L1" t="n">
-        <v>-49.22772216796875</v>
+        <v>-76.96833801269531</v>
       </c>
       <c r="M1" t="n">
-        <v>-52.23255157470703</v>
+        <v>-75.33214569091797</v>
       </c>
       <c r="N1" t="n">
-        <v>-49.55915832519531</v>
+        <v>-84.37239074707031</v>
       </c>
       <c r="O1" t="n">
-        <v>-59.906982421875</v>
+        <v>-76.30832672119141</v>
       </c>
       <c r="P1" t="n">
-        <v>-57.49440383911133</v>
+        <v>-61.59439086914062</v>
       </c>
       <c r="Q1" t="n">
-        <v>-57.68484497070312</v>
+        <v>-77.27507019042969</v>
       </c>
       <c r="R1" t="n">
-        <v>-60.36186981201172</v>
+        <v>-61.89092254638672</v>
       </c>
       <c r="S1" t="n">
-        <v>-59.3839111328125</v>
+        <v>-76.43122100830078</v>
       </c>
       <c r="T1" t="n">
-        <v>-61.32760620117188</v>
+        <v>-64.86000823974609</v>
       </c>
       <c r="U1" t="n">
-        <v>-61.9827995300293</v>
+        <v>-62.80081176757812</v>
       </c>
       <c r="V1" t="n">
-        <v>-63.02618408203125</v>
+        <v>-64.84786987304688</v>
       </c>
       <c r="W1" t="n">
-        <v>-60.37679290771484</v>
+        <v>-72.52680206298828</v>
       </c>
       <c r="X1" t="n">
-        <v>-59.48674774169922</v>
+        <v>-68.18289184570312</v>
       </c>
       <c r="Y1" t="n">
-        <v>-58.66250610351562</v>
+        <v>-76.41941833496094</v>
       </c>
       <c r="Z1" t="n">
-        <v>-65.19953155517578</v>
+        <v>-60.95967483520508</v>
       </c>
       <c r="AA1" t="n">
-        <v>-64.79994201660156</v>
+        <v>-60.04459381103516</v>
       </c>
       <c r="AB1" t="n">
-        <v>-57.68716430664062</v>
+        <v>-71.96694946289062</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>-32.04389190673828</v>
+        <v>-74.80229187011719</v>
       </c>
       <c r="B2" t="n">
-        <v>-34.67810821533203</v>
+        <v>-74.64337158203125</v>
       </c>
       <c r="C2" t="n">
-        <v>-38.67903900146484</v>
+        <v>-69.90362548828125</v>
       </c>
       <c r="D2" t="n">
-        <v>-35.78197479248047</v>
+        <v>-73.71751403808594</v>
       </c>
       <c r="E2" t="n">
-        <v>-40.62976837158203</v>
+        <v>-83.56559753417969</v>
       </c>
       <c r="F2" t="n">
-        <v>-40.52050018310547</v>
+        <v>-68.77293395996094</v>
       </c>
       <c r="G2" t="n">
-        <v>-42.69593811035156</v>
+        <v>-78.66440582275391</v>
       </c>
       <c r="H2" t="n">
-        <v>-43.75606536865234</v>
+        <v>-76.76664733886719</v>
       </c>
       <c r="I2" t="n">
-        <v>-45.29669952392578</v>
+        <v>-82.69882965087891</v>
       </c>
       <c r="J2" t="n">
-        <v>-47.22108840942383</v>
+        <v>-82.84363555908203</v>
       </c>
       <c r="K2" t="n">
-        <v>-46.93954086303711</v>
+        <v>-72.24796295166016</v>
       </c>
       <c r="L2" t="n">
-        <v>-45.29971694946289</v>
+        <v>-72.36660003662109</v>
       </c>
       <c r="M2" t="n">
-        <v>-51.40987396240234</v>
+        <v>-72.41321563720703</v>
       </c>
       <c r="N2" t="n">
-        <v>-46.93362808227539</v>
+        <v>-65.20472717285156</v>
       </c>
       <c r="O2" t="n">
-        <v>-59.56643676757812</v>
+        <v>-90.42746734619141</v>
       </c>
       <c r="P2" t="n">
-        <v>-60.7562141418457</v>
+        <v>-63.81684494018555</v>
       </c>
       <c r="Q2" t="n">
-        <v>-62.73332595825195</v>
+        <v>-71.18580627441406</v>
       </c>
       <c r="R2" t="n">
-        <v>-60.45221710205078</v>
+        <v>-85.74565124511719</v>
       </c>
       <c r="S2" t="n">
-        <v>-57.48945236206055</v>
+        <v>-81.21646118164062</v>
       </c>
       <c r="T2" t="n">
-        <v>-59.64780807495117</v>
+        <v>-72.14297485351562</v>
       </c>
       <c r="U2" t="n">
-        <v>-58.69869995117188</v>
+        <v>-75.24336242675781</v>
       </c>
       <c r="V2" t="n">
-        <v>-60.96691131591797</v>
+        <v>-59.89518356323242</v>
       </c>
       <c r="W2" t="n">
-        <v>-63.61768341064453</v>
+        <v>-75.92411804199219</v>
       </c>
       <c r="X2" t="n">
-        <v>-62.51157760620117</v>
+        <v>-85.84056091308594</v>
       </c>
       <c r="Y2" t="n">
-        <v>-61.7217903137207</v>
+        <v>-76.68846130371094</v>
       </c>
       <c r="Z2" t="n">
-        <v>-60.81198120117188</v>
+        <v>-75.92701721191406</v>
       </c>
       <c r="AA2" t="n">
-        <v>-67.11181640625</v>
+        <v>-65.71364593505859</v>
       </c>
       <c r="AB2" t="n">
-        <v>-64.61109924316406</v>
+        <v>-76.30552673339844</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>-37.27218627929688</v>
+        <v>-91.19414520263672</v>
       </c>
       <c r="B3" t="n">
-        <v>-31.8060359954834</v>
+        <v>-71.21761322021484</v>
       </c>
       <c r="C3" t="n">
-        <v>-43.2800178527832</v>
+        <v>-70.32964324951172</v>
       </c>
       <c r="D3" t="n">
-        <v>-40.42201232910156</v>
+        <v>-67.53705596923828</v>
       </c>
       <c r="E3" t="n">
-        <v>-42.87697601318359</v>
+        <v>-84.78644561767578</v>
       </c>
       <c r="F3" t="n">
-        <v>-44.81167984008789</v>
+        <v>-74.03256988525391</v>
       </c>
       <c r="G3" t="n">
-        <v>-48.03738021850586</v>
+        <v>-78.81375885009766</v>
       </c>
       <c r="H3" t="n">
-        <v>-42.216064453125</v>
+        <v>-83.50215148925781</v>
       </c>
       <c r="I3" t="n">
-        <v>-44.46630859375</v>
+        <v>-66.26586151123047</v>
       </c>
       <c r="J3" t="n">
-        <v>-46.60549163818359</v>
+        <v>-88.14238739013672</v>
       </c>
       <c r="K3" t="n">
-        <v>-47.93185806274414</v>
+        <v>-93.73645782470703</v>
       </c>
       <c r="L3" t="n">
-        <v>-48.24081420898438</v>
+        <v>-57.78604125976562</v>
       </c>
       <c r="M3" t="n">
-        <v>-46.21883010864258</v>
+        <v>-90.32112884521484</v>
       </c>
       <c r="N3" t="n">
-        <v>-48.70598983764648</v>
+        <v>-75.586669921875</v>
       </c>
       <c r="O3" t="n">
-        <v>-56.06248092651367</v>
+        <v>-84.14304351806641</v>
       </c>
       <c r="P3" t="n">
-        <v>-62.41753005981445</v>
+        <v>-87.15025329589844</v>
       </c>
       <c r="Q3" t="n">
-        <v>-61.62591552734375</v>
+        <v>-86.62138366699219</v>
       </c>
       <c r="R3" t="n">
-        <v>-59.5455207824707</v>
+        <v>-76.49436187744141</v>
       </c>
       <c r="S3" t="n">
-        <v>-61.0350456237793</v>
+        <v>-85.62516784667969</v>
       </c>
       <c r="T3" t="n">
-        <v>-59.58895111083984</v>
+        <v>-83.55770874023438</v>
       </c>
       <c r="U3" t="n">
-        <v>-62.75980758666992</v>
+        <v>-91.70990753173828</v>
       </c>
       <c r="V3" t="n">
-        <v>-57.65962600708008</v>
+        <v>-87.92328643798828</v>
       </c>
       <c r="W3" t="n">
-        <v>-65.25523376464844</v>
+        <v>-90.28951263427734</v>
       </c>
       <c r="X3" t="n">
-        <v>-59.61018753051758</v>
+        <v>-76.16940307617188</v>
       </c>
       <c r="Y3" t="n">
-        <v>-65.16635894775391</v>
+        <v>-81.63181304931641</v>
       </c>
       <c r="Z3" t="n">
-        <v>-61.68604278564453</v>
+        <v>-68.26722717285156</v>
       </c>
       <c r="AA3" t="n">
-        <v>-58.04499435424805</v>
+        <v>-75.73928070068359</v>
       </c>
       <c r="AB3" t="n">
-        <v>-61.70449066162109</v>
+        <v>-58.99312591552734</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>-34.3663330078125</v>
+        <v>-87.59547424316406</v>
       </c>
       <c r="B4" t="n">
-        <v>-35.84346008300781</v>
+        <v>-64.04345703125</v>
       </c>
       <c r="C4" t="n">
-        <v>-37.58388519287109</v>
+        <v>-81.24237060546875</v>
       </c>
       <c r="D4" t="n">
-        <v>-39.21319198608398</v>
+        <v>-71.91827392578125</v>
       </c>
       <c r="E4" t="n">
-        <v>-41.94296646118164</v>
+        <v>-74.33203887939453</v>
       </c>
       <c r="F4" t="n">
-        <v>-41.88603591918945</v>
+        <v>-63.13004302978516</v>
       </c>
       <c r="G4" t="n">
-        <v>-45.60376739501953</v>
+        <v>-91.83712768554688</v>
       </c>
       <c r="H4" t="n">
-        <v>-42.00543594360352</v>
+        <v>-81.89439392089844</v>
       </c>
       <c r="I4" t="n">
-        <v>-45.18780899047852</v>
+        <v>-78.63700866699219</v>
       </c>
       <c r="J4" t="n">
-        <v>-46.09293365478516</v>
+        <v>-68.66731262207031</v>
       </c>
       <c r="K4" t="n">
-        <v>-44.4974365234375</v>
+        <v>-70.64402770996094</v>
       </c>
       <c r="L4" t="n">
-        <v>-46.93883895874023</v>
+        <v>-56.28509521484375</v>
       </c>
       <c r="M4" t="n">
-        <v>-49.64777374267578</v>
+        <v>-82.21013641357422</v>
       </c>
       <c r="N4" t="n">
-        <v>-46.68128204345703</v>
+        <v>-76.44357299804688</v>
       </c>
       <c r="O4" t="n">
-        <v>-58.22520065307617</v>
+        <v>-88.0999755859375</v>
       </c>
       <c r="P4" t="n">
-        <v>-60.38124465942383</v>
+        <v>-67.67652130126953</v>
       </c>
       <c r="Q4" t="n">
-        <v>-61.67075729370117</v>
+        <v>-86.19740295410156</v>
       </c>
       <c r="R4" t="n">
-        <v>-60.2586555480957</v>
+        <v>-73.62579345703125</v>
       </c>
       <c r="S4" t="n">
-        <v>-58.91646194458008</v>
+        <v>-74.27568054199219</v>
       </c>
       <c r="T4" t="n">
-        <v>-59.21928787231445</v>
+        <v>-67.77785491943359</v>
       </c>
       <c r="U4" t="n">
-        <v>-61.57860565185547</v>
+        <v>-85.18325805664062</v>
       </c>
       <c r="V4" t="n">
-        <v>-59.22674560546875</v>
+        <v>-71.94036102294922</v>
       </c>
       <c r="W4" t="n">
-        <v>-60.96737670898438</v>
+        <v>-89.17828369140625</v>
       </c>
       <c r="X4" t="n">
-        <v>-60.86006546020508</v>
+        <v>-75.27013397216797</v>
       </c>
       <c r="Y4" t="n">
-        <v>-61.68556976318359</v>
+        <v>-83.82188415527344</v>
       </c>
       <c r="Z4" t="n">
-        <v>-61.88519287109375</v>
+        <v>-70.85688781738281</v>
       </c>
       <c r="AA4" t="n">
-        <v>-62.0846061706543</v>
+        <v>-74.57997894287109</v>
       </c>
       <c r="AB4" t="n">
-        <v>-61.82863235473633</v>
+        <v>-51.17017364501953</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>-39.24611282348633</v>
+        <v>-79.466796875</v>
       </c>
       <c r="B5" t="n">
-        <v>-42.6827507019043</v>
+        <v>-62.02902984619141</v>
       </c>
       <c r="C5" t="n">
-        <v>-40.10779190063477</v>
+        <v>-85.56533813476562</v>
       </c>
       <c r="D5" t="n">
-        <v>-41.78126907348633</v>
+        <v>-76.32939147949219</v>
       </c>
       <c r="E5" t="n">
-        <v>-42.92636108398438</v>
+        <v>-83.63775634765625</v>
       </c>
       <c r="F5" t="n">
-        <v>-42.04838562011719</v>
+        <v>-83.15855407714844</v>
       </c>
       <c r="G5" t="n">
-        <v>-45.16454315185547</v>
+        <v>-77.32174682617188</v>
       </c>
       <c r="H5" t="n">
-        <v>-48.1346321105957</v>
+        <v>-79.04362487792969</v>
       </c>
       <c r="I5" t="n">
-        <v>-47.84298324584961</v>
+        <v>-81.58033752441406</v>
       </c>
       <c r="J5" t="n">
-        <v>-50.32376098632812</v>
+        <v>-74.11294555664062</v>
       </c>
       <c r="K5" t="n">
-        <v>-46.82309722900391</v>
+        <v>-85.28550720214844</v>
       </c>
       <c r="L5" t="n">
-        <v>-47.89774322509766</v>
+        <v>-90.96086120605469</v>
       </c>
       <c r="M5" t="n">
-        <v>-47.81772613525391</v>
+        <v>-81.09257507324219</v>
       </c>
       <c r="N5" t="n">
-        <v>-49.94095993041992</v>
+        <v>-76.44484710693359</v>
       </c>
       <c r="O5" t="n">
-        <v>-57.68596267700195</v>
+        <v>-88.79289245605469</v>
       </c>
       <c r="P5" t="n">
-        <v>-60.67438507080078</v>
+        <v>-82.42304992675781</v>
       </c>
       <c r="Q5" t="n">
-        <v>-59.53209686279297</v>
+        <v>-79.06007385253906</v>
       </c>
       <c r="R5" t="n">
-        <v>-56.69467163085938</v>
+        <v>-86.79144287109375</v>
       </c>
       <c r="S5" t="n">
-        <v>-57.00820922851562</v>
+        <v>-87.2442626953125</v>
       </c>
       <c r="T5" t="n">
-        <v>-61.3116569519043</v>
+        <v>-86.72503662109375</v>
       </c>
       <c r="U5" t="n">
-        <v>-58.89592742919922</v>
+        <v>-97.08396148681641</v>
       </c>
       <c r="V5" t="n">
-        <v>-59.26461791992188</v>
+        <v>-90.15705871582031</v>
       </c>
       <c r="W5" t="n">
-        <v>-63.12590408325195</v>
+        <v>-87.95698547363281</v>
       </c>
       <c r="X5" t="n">
-        <v>-65.48952484130859</v>
+        <v>-82.48434448242188</v>
       </c>
       <c r="Y5" t="n">
-        <v>-57.36296463012695</v>
+        <v>-83.18124389648438</v>
       </c>
       <c r="Z5" t="n">
-        <v>-65.51957702636719</v>
+        <v>-80.84592437744141</v>
       </c>
       <c r="AA5" t="n">
-        <v>-61.8925895690918</v>
+        <v>-74.31261444091797</v>
       </c>
       <c r="AB5" t="n">
-        <v>-60.97856521606445</v>
+        <v>-66.00648498535156</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>-38.80415725708008</v>
+        <v>-67.77919006347656</v>
       </c>
       <c r="B6" t="n">
-        <v>-40.3068962097168</v>
+        <v>-57.95932006835938</v>
       </c>
       <c r="C6" t="n">
-        <v>-46.0603141784668</v>
+        <v>-87.27537536621094</v>
       </c>
       <c r="D6" t="n">
-        <v>-38.76701354980469</v>
+        <v>-62.43320465087891</v>
       </c>
       <c r="E6" t="n">
-        <v>-45.36397171020508</v>
+        <v>-77.71372985839844</v>
       </c>
       <c r="F6" t="n">
-        <v>-40.14743423461914</v>
+        <v>-61.97048950195312</v>
       </c>
       <c r="G6" t="n">
-        <v>-47.9378662109375</v>
+        <v>-91.84098815917969</v>
       </c>
       <c r="H6" t="n">
-        <v>-44.75962066650391</v>
+        <v>-62.49015045166016</v>
       </c>
       <c r="I6" t="n">
-        <v>-48.70655822753906</v>
+        <v>-86.41314697265625</v>
       </c>
       <c r="J6" t="n">
-        <v>-43.95630645751953</v>
+        <v>-80.98637390136719</v>
       </c>
       <c r="K6" t="n">
-        <v>-47.86000442504883</v>
+        <v>-71.38374328613281</v>
       </c>
       <c r="L6" t="n">
-        <v>-48.51444625854492</v>
+        <v>-68.456298828125</v>
       </c>
       <c r="M6" t="n">
-        <v>-48.64750671386719</v>
+        <v>-71.26861572265625</v>
       </c>
       <c r="N6" t="n">
-        <v>-50.07915496826172</v>
+        <v>-61.20488739013672</v>
       </c>
       <c r="O6" t="n">
-        <v>-63.40360260009766</v>
+        <v>-86.64793395996094</v>
       </c>
       <c r="P6" t="n">
-        <v>-58.65459060668945</v>
+        <v>-76.03868103027344</v>
       </c>
       <c r="Q6" t="n">
-        <v>-57.72246170043945</v>
+        <v>-81.85777282714844</v>
       </c>
       <c r="R6" t="n">
-        <v>-59.52432250976562</v>
+        <v>-62.35752487182617</v>
       </c>
       <c r="S6" t="n">
-        <v>-58.80788421630859</v>
+        <v>-89.54006195068359</v>
       </c>
       <c r="T6" t="n">
-        <v>-59.74413299560547</v>
+        <v>-57.33104705810547</v>
       </c>
       <c r="U6" t="n">
-        <v>-57.33131790161133</v>
+        <v>-77.37593078613281</v>
       </c>
       <c r="V6" t="n">
-        <v>-63.73579025268555</v>
+        <v>-64.0570068359375</v>
       </c>
       <c r="W6" t="n">
-        <v>-59.11486053466797</v>
+        <v>-84.03239440917969</v>
       </c>
       <c r="X6" t="n">
-        <v>-59.87062454223633</v>
+        <v>-68.40278625488281</v>
       </c>
       <c r="Y6" t="n">
-        <v>-64.15976715087891</v>
+        <v>-75.83815002441406</v>
       </c>
       <c r="Z6" t="n">
-        <v>-60.43444061279297</v>
+        <v>-73.12712097167969</v>
       </c>
       <c r="AA6" t="n">
-        <v>-62.66865158081055</v>
+        <v>-66.32987976074219</v>
       </c>
       <c r="AB6" t="n">
-        <v>-64.04458618164062</v>
+        <v>-79.73634338378906</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>-46.45972442626953</v>
+        <v>-75.88029479980469</v>
       </c>
       <c r="B7" t="n">
-        <v>-43.97828674316406</v>
+        <v>-75.58793640136719</v>
       </c>
       <c r="C7" t="n">
-        <v>-40.87051391601562</v>
+        <v>-76.85543823242188</v>
       </c>
       <c r="D7" t="n">
-        <v>-47.1096076965332</v>
+        <v>-75.41356658935547</v>
       </c>
       <c r="E7" t="n">
-        <v>-41.9774169921875</v>
+        <v>-80.10748291015625</v>
       </c>
       <c r="F7" t="n">
-        <v>-41.25973892211914</v>
+        <v>-78.22190856933594</v>
       </c>
       <c r="G7" t="n">
-        <v>-46.96743011474609</v>
+        <v>-88.58516693115234</v>
       </c>
       <c r="H7" t="n">
-        <v>-48.81289672851562</v>
+        <v>-86.80513000488281</v>
       </c>
       <c r="I7" t="n">
-        <v>-48.53176879882812</v>
+        <v>-91.02279663085938</v>
       </c>
       <c r="J7" t="n">
-        <v>-45.32663726806641</v>
+        <v>-91.55856323242188</v>
       </c>
       <c r="K7" t="n">
-        <v>-50.07865142822266</v>
+        <v>-88.26737976074219</v>
       </c>
       <c r="L7" t="n">
-        <v>-50.62560653686523</v>
+        <v>-89.01411437988281</v>
       </c>
       <c r="M7" t="n">
-        <v>-51.32152557373047</v>
+        <v>-81.70393371582031</v>
       </c>
       <c r="N7" t="n">
-        <v>-49.41916275024414</v>
+        <v>-93.79084014892578</v>
       </c>
       <c r="O7" t="n">
-        <v>-59.79302978515625</v>
+        <v>-78.02641296386719</v>
       </c>
       <c r="P7" t="n">
-        <v>-62.44355392456055</v>
+        <v>-82.99501037597656</v>
       </c>
       <c r="Q7" t="n">
-        <v>-58.99993896484375</v>
+        <v>-86.44654846191406</v>
       </c>
       <c r="R7" t="n">
-        <v>-60.8080940246582</v>
+        <v>-84.63208770751953</v>
       </c>
       <c r="S7" t="n">
-        <v>-63.64304351806641</v>
+        <v>-87.43797302246094</v>
       </c>
       <c r="T7" t="n">
-        <v>-62.61821365356445</v>
+        <v>-94.72769927978516</v>
       </c>
       <c r="U7" t="n">
-        <v>-65.21926116943359</v>
+        <v>-89.41500854492188</v>
       </c>
       <c r="V7" t="n">
-        <v>-59.7933235168457</v>
+        <v>-78.23134613037109</v>
       </c>
       <c r="W7" t="n">
-        <v>-63.25874710083008</v>
+        <v>-94.34867095947266</v>
       </c>
       <c r="X7" t="n">
-        <v>-63.55784225463867</v>
+        <v>-76.34171295166016</v>
       </c>
       <c r="Y7" t="n">
-        <v>-61.76145553588867</v>
+        <v>-80.34656524658203</v>
       </c>
       <c r="Z7" t="n">
-        <v>-62.95607757568359</v>
+        <v>-81.61338043212891</v>
       </c>
       <c r="AA7" t="n">
-        <v>-65.93304443359375</v>
+        <v>-64.28102874755859</v>
       </c>
       <c r="AB7" t="n">
-        <v>-63.50859451293945</v>
+        <v>-74.99307250976562</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>-44.11029434204102</v>
+        <v>-75.44401550292969</v>
       </c>
       <c r="B8" t="n">
-        <v>-43.02178955078125</v>
+        <v>-59.6003303527832</v>
       </c>
       <c r="C8" t="n">
-        <v>-40.51861572265625</v>
+        <v>-96.816162109375</v>
       </c>
       <c r="D8" t="n">
-        <v>-44.88571166992188</v>
+        <v>-60.10636138916016</v>
       </c>
       <c r="E8" t="n">
-        <v>-46.95612335205078</v>
+        <v>-85.00899505615234</v>
       </c>
       <c r="F8" t="n">
-        <v>-45.04131317138672</v>
+        <v>-76.34477233886719</v>
       </c>
       <c r="G8" t="n">
-        <v>-42.99966049194336</v>
+        <v>-78.18250274658203</v>
       </c>
       <c r="H8" t="n">
-        <v>-48.21672821044922</v>
+        <v>-79.48410034179688</v>
       </c>
       <c r="I8" t="n">
-        <v>-45.11962127685547</v>
+        <v>-74.58659362792969</v>
       </c>
       <c r="J8" t="n">
-        <v>-50.32101440429688</v>
+        <v>-68.75617980957031</v>
       </c>
       <c r="K8" t="n">
-        <v>-49.07780075073242</v>
+        <v>-84.34958648681641</v>
       </c>
       <c r="L8" t="n">
-        <v>-52.92393112182617</v>
+        <v>-65.91478729248047</v>
       </c>
       <c r="M8" t="n">
-        <v>-46.39355850219727</v>
+        <v>-88.12776184082031</v>
       </c>
       <c r="N8" t="n">
-        <v>-48.70112991333008</v>
+        <v>-61.17745971679688</v>
       </c>
       <c r="O8" t="n">
-        <v>-56.52497100830078</v>
+        <v>-84.18527984619141</v>
       </c>
       <c r="P8" t="n">
-        <v>-57.3201789855957</v>
+        <v>-62.50463104248047</v>
       </c>
       <c r="Q8" t="n">
-        <v>-65.54426574707031</v>
+        <v>-85.21433258056641</v>
       </c>
       <c r="R8" t="n">
-        <v>-60.66512298583984</v>
+        <v>-63.23707962036133</v>
       </c>
       <c r="S8" t="n">
-        <v>-60.18657684326172</v>
+        <v>-70.77994537353516</v>
       </c>
       <c r="T8" t="n">
-        <v>-61.74723052978516</v>
+        <v>-71.82734680175781</v>
       </c>
       <c r="U8" t="n">
-        <v>-60.6794319152832</v>
+        <v>-78.66896057128906</v>
       </c>
       <c r="V8" t="n">
-        <v>-61.99364471435547</v>
+        <v>-48.16135025024414</v>
       </c>
       <c r="W8" t="n">
-        <v>-60.88182830810547</v>
+        <v>-77.41866302490234</v>
       </c>
       <c r="X8" t="n">
-        <v>-64.91239166259766</v>
+        <v>-78.90360260009766</v>
       </c>
       <c r="Y8" t="n">
-        <v>-62.16561126708984</v>
+        <v>-88.59636688232422</v>
       </c>
       <c r="Z8" t="n">
-        <v>-67.05184936523438</v>
+        <v>-76.67459869384766</v>
       </c>
       <c r="AA8" t="n">
-        <v>-60.51767730712891</v>
+        <v>-75.17497253417969</v>
       </c>
       <c r="AB8" t="n">
-        <v>-65.27511596679688</v>
+        <v>-45.76862335205078</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>-47.51956176757812</v>
+        <v>-74.58746337890625</v>
       </c>
       <c r="B9" t="n">
-        <v>-47.00323486328125</v>
+        <v>-80.75263977050781</v>
       </c>
       <c r="C9" t="n">
-        <v>-46.21758270263672</v>
+        <v>-72.18035125732422</v>
       </c>
       <c r="D9" t="n">
-        <v>-42.31058883666992</v>
+        <v>-76.76568603515625</v>
       </c>
       <c r="E9" t="n">
-        <v>-46.37199783325195</v>
+        <v>-85.97775268554688</v>
       </c>
       <c r="F9" t="n">
-        <v>-47.60813140869141</v>
+        <v>-82.93617248535156</v>
       </c>
       <c r="G9" t="n">
-        <v>-47.86042785644531</v>
+        <v>-88.74119567871094</v>
       </c>
       <c r="H9" t="n">
-        <v>-48.47309112548828</v>
+        <v>-72.99072265625</v>
       </c>
       <c r="I9" t="n">
-        <v>-43.34632110595703</v>
+        <v>-91.88827514648438</v>
       </c>
       <c r="J9" t="n">
-        <v>-49.09670257568359</v>
+        <v>-70.9320068359375</v>
       </c>
       <c r="K9" t="n">
-        <v>-46.19596862792969</v>
+        <v>-86.97446441650391</v>
       </c>
       <c r="L9" t="n">
-        <v>-56.1611213684082</v>
+        <v>-85.38876342773438</v>
       </c>
       <c r="M9" t="n">
-        <v>-47.44516754150391</v>
+        <v>-78.50801849365234</v>
       </c>
       <c r="N9" t="n">
-        <v>-50.44439697265625</v>
+        <v>-83.07118225097656</v>
       </c>
       <c r="O9" t="n">
-        <v>-57.81386566162109</v>
+        <v>-85.22675323486328</v>
       </c>
       <c r="P9" t="n">
-        <v>-60.52445602416992</v>
+        <v>-85.95768737792969</v>
       </c>
       <c r="Q9" t="n">
-        <v>-58.96533203125</v>
+        <v>-81.95039367675781</v>
       </c>
       <c r="R9" t="n">
-        <v>-59.02616500854492</v>
+        <v>-78.53755950927734</v>
       </c>
       <c r="S9" t="n">
-        <v>-63.63665008544922</v>
+        <v>-89.25402069091797</v>
       </c>
       <c r="T9" t="n">
-        <v>-63.2293815612793</v>
+        <v>-81.22231292724609</v>
       </c>
       <c r="U9" t="n">
-        <v>-60.27592849731445</v>
+        <v>-81.16056060791016</v>
       </c>
       <c r="V9" t="n">
-        <v>-62.10132598876953</v>
+        <v>-90.56086730957031</v>
       </c>
       <c r="W9" t="n">
-        <v>-64.83116912841797</v>
+        <v>-83.21464538574219</v>
       </c>
       <c r="X9" t="n">
-        <v>-62.5146369934082</v>
+        <v>-86.85508728027344</v>
       </c>
       <c r="Y9" t="n">
-        <v>-63.03199005126953</v>
+        <v>-83.81455993652344</v>
       </c>
       <c r="Z9" t="n">
-        <v>-64.0809326171875</v>
+        <v>-67.16458129882812</v>
       </c>
       <c r="AA9" t="n">
-        <v>-64.20045471191406</v>
+        <v>-64.36415863037109</v>
       </c>
       <c r="AB9" t="n">
-        <v>-61.88530349731445</v>
+        <v>-81.68099212646484</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>-45.70144271850586</v>
+        <v>-75.93390655517578</v>
       </c>
       <c r="B10" t="n">
-        <v>-43.50876998901367</v>
+        <v>-55.0559196472168</v>
       </c>
       <c r="C10" t="n">
-        <v>-43.29996490478516</v>
+        <v>-79.83956146240234</v>
       </c>
       <c r="D10" t="n">
-        <v>-43.22845840454102</v>
+        <v>-62.0485725402832</v>
       </c>
       <c r="E10" t="n">
-        <v>-45.06451416015625</v>
+        <v>-87.11618804931641</v>
       </c>
       <c r="F10" t="n">
-        <v>-52.4586067199707</v>
+        <v>-72.52489471435547</v>
       </c>
       <c r="G10" t="n">
-        <v>-45.59206008911133</v>
+        <v>-89.0369873046875</v>
       </c>
       <c r="H10" t="n">
-        <v>-52.65116119384766</v>
+        <v>-60.77904510498047</v>
       </c>
       <c r="I10" t="n">
-        <v>-45.59468841552734</v>
+        <v>-71.02566528320312</v>
       </c>
       <c r="J10" t="n">
-        <v>-46.64960861206055</v>
+        <v>-65.74324035644531</v>
       </c>
       <c r="K10" t="n">
-        <v>-51.16498947143555</v>
+        <v>-83.7515869140625</v>
       </c>
       <c r="L10" t="n">
-        <v>-52.35969161987305</v>
+        <v>-67.59534454345703</v>
       </c>
       <c r="M10" t="n">
-        <v>-46.50264358520508</v>
+        <v>-84.25849151611328</v>
       </c>
       <c r="N10" t="n">
-        <v>-47.50825119018555</v>
+        <v>-63.79903411865234</v>
       </c>
       <c r="O10" t="n">
-        <v>-61.21223068237305</v>
+        <v>-90.02684020996094</v>
       </c>
       <c r="P10" t="n">
-        <v>-58.47578048706055</v>
+        <v>-62.29844284057617</v>
       </c>
       <c r="Q10" t="n">
-        <v>-63.17559051513672</v>
+        <v>-83.61869049072266</v>
       </c>
       <c r="R10" t="n">
-        <v>-62.4737663269043</v>
+        <v>-68.09871673583984</v>
       </c>
       <c r="S10" t="n">
-        <v>-63.54306030273438</v>
+        <v>-94.02777099609375</v>
       </c>
       <c r="T10" t="n">
-        <v>-65.01622009277344</v>
+        <v>-70.19270324707031</v>
       </c>
       <c r="U10" t="n">
-        <v>-62.77954864501953</v>
+        <v>-71.79057312011719</v>
       </c>
       <c r="V10" t="n">
-        <v>-62.17535400390625</v>
+        <v>-67.28302764892578</v>
       </c>
       <c r="W10" t="n">
-        <v>-61.38029098510742</v>
+        <v>-82.13710021972656</v>
       </c>
       <c r="X10" t="n">
-        <v>-62.83157348632812</v>
+        <v>-69.78224182128906</v>
       </c>
       <c r="Y10" t="n">
-        <v>-61.08866500854492</v>
+        <v>-82.70664215087891</v>
       </c>
       <c r="Z10" t="n">
-        <v>-60.81101226806641</v>
+        <v>-58.83246612548828</v>
       </c>
       <c r="AA10" t="n">
-        <v>-60.31439971923828</v>
+        <v>-76.37110900878906</v>
       </c>
       <c r="AB10" t="n">
-        <v>-64.09152984619141</v>
+        <v>-58.74900436401367</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>-39.86916351318359</v>
+        <v>-69.80665588378906</v>
       </c>
       <c r="B11" t="n">
-        <v>-45.35436248779297</v>
+        <v>-53.960693359375</v>
       </c>
       <c r="C11" t="n">
-        <v>-45.10792922973633</v>
+        <v>-86.23993682861328</v>
       </c>
       <c r="D11" t="n">
-        <v>-46.40155029296875</v>
+        <v>-80.25316619873047</v>
       </c>
       <c r="E11" t="n">
-        <v>-43.59577560424805</v>
+        <v>-81.81566619873047</v>
       </c>
       <c r="F11" t="n">
-        <v>-46.88069534301758</v>
+        <v>-81.40243530273438</v>
       </c>
       <c r="G11" t="n">
-        <v>-48.33383178710938</v>
+        <v>-80.6409912109375</v>
       </c>
       <c r="H11" t="n">
-        <v>-47.84434127807617</v>
+        <v>-85.90396881103516</v>
       </c>
       <c r="I11" t="n">
-        <v>-49.30593872070312</v>
+        <v>-73.65909576416016</v>
       </c>
       <c r="J11" t="n">
-        <v>-48.92707443237305</v>
+        <v>-75.74605560302734</v>
       </c>
       <c r="K11" t="n">
-        <v>-45.98738861083984</v>
+        <v>-83.72770690917969</v>
       </c>
       <c r="L11" t="n">
-        <v>-49.28255462646484</v>
+        <v>-82.63835906982422</v>
       </c>
       <c r="M11" t="n">
-        <v>-45.60257720947266</v>
+        <v>-90.23866271972656</v>
       </c>
       <c r="N11" t="n">
-        <v>-50.20646286010742</v>
+        <v>-84.10463714599609</v>
       </c>
       <c r="O11" t="n">
-        <v>-60.05587768554688</v>
+        <v>-86.75882720947266</v>
       </c>
       <c r="P11" t="n">
-        <v>-61.36737060546875</v>
+        <v>-86.99912261962891</v>
       </c>
       <c r="Q11" t="n">
-        <v>-61.1683464050293</v>
+        <v>-93.41429901123047</v>
       </c>
       <c r="R11" t="n">
-        <v>-62.13722610473633</v>
+        <v>-86.664794921875</v>
       </c>
       <c r="S11" t="n">
-        <v>-62.04412078857422</v>
+        <v>-74.23148345947266</v>
       </c>
       <c r="T11" t="n">
-        <v>-58.86861038208008</v>
+        <v>-82.24935150146484</v>
       </c>
       <c r="U11" t="n">
-        <v>-62.44779205322266</v>
+        <v>-84.90280151367188</v>
       </c>
       <c r="V11" t="n">
-        <v>-58.37010955810547</v>
+        <v>-82.33829498291016</v>
       </c>
       <c r="W11" t="n">
-        <v>-67.47460174560547</v>
+        <v>-83.52491760253906</v>
       </c>
       <c r="X11" t="n">
-        <v>-64.21963500976562</v>
+        <v>-76.08204650878906</v>
       </c>
       <c r="Y11" t="n">
-        <v>-62.06607055664062</v>
+        <v>-86.83329772949219</v>
       </c>
       <c r="Z11" t="n">
-        <v>-61.42173004150391</v>
+        <v>-73.08400726318359</v>
       </c>
       <c r="AA11" t="n">
-        <v>-65.15987396240234</v>
+        <v>-71.93446350097656</v>
       </c>
       <c r="AB11" t="n">
-        <v>-64.4459228515625</v>
+        <v>-80.63686370849609</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>-49.69390869140625</v>
+        <v>-79.90589904785156</v>
       </c>
       <c r="B12" t="n">
-        <v>-48.66730499267578</v>
+        <v>-42.79199981689453</v>
       </c>
       <c r="C12" t="n">
-        <v>-48.5210075378418</v>
+        <v>-79.19429016113281</v>
       </c>
       <c r="D12" t="n">
-        <v>-52.5930290222168</v>
+        <v>-61.86185455322266</v>
       </c>
       <c r="E12" t="n">
-        <v>-50.30340957641602</v>
+        <v>-90.93117523193359</v>
       </c>
       <c r="F12" t="n">
-        <v>-49.66489410400391</v>
+        <v>-66.51075744628906</v>
       </c>
       <c r="G12" t="n">
-        <v>-46.38806915283203</v>
+        <v>-77.92241668701172</v>
       </c>
       <c r="H12" t="n">
-        <v>-47.04332733154297</v>
+        <v>-65.49997711181641</v>
       </c>
       <c r="I12" t="n">
-        <v>-45.62741851806641</v>
+        <v>-85.96600341796875</v>
       </c>
       <c r="J12" t="n">
-        <v>-47.66294097900391</v>
+        <v>-62.43619537353516</v>
       </c>
       <c r="K12" t="n">
-        <v>-53.38933563232422</v>
+        <v>-86.59159851074219</v>
       </c>
       <c r="L12" t="n">
-        <v>-50.64566421508789</v>
+        <v>-74.57839202880859</v>
       </c>
       <c r="M12" t="n">
-        <v>-48.87991333007812</v>
+        <v>-85.86219787597656</v>
       </c>
       <c r="N12" t="n">
-        <v>-50.55191802978516</v>
+        <v>-71.10971832275391</v>
       </c>
       <c r="O12" t="n">
-        <v>-59.90559005737305</v>
+        <v>-83.060546875</v>
       </c>
       <c r="P12" t="n">
-        <v>-58.58148193359375</v>
+        <v>-74.78617095947266</v>
       </c>
       <c r="Q12" t="n">
-        <v>-58.28556060791016</v>
+        <v>-74.86422729492188</v>
       </c>
       <c r="R12" t="n">
-        <v>-57.04994583129883</v>
+        <v>-83.67570495605469</v>
       </c>
       <c r="S12" t="n">
-        <v>-63.23323440551758</v>
+        <v>-75.96576690673828</v>
       </c>
       <c r="T12" t="n">
-        <v>-60.8824577331543</v>
+        <v>-71.83893585205078</v>
       </c>
       <c r="U12" t="n">
-        <v>-62.32122802734375</v>
+        <v>-86.4027099609375</v>
       </c>
       <c r="V12" t="n">
-        <v>-58.58622360229492</v>
+        <v>-72.57008361816406</v>
       </c>
       <c r="W12" t="n">
-        <v>-62.26702880859375</v>
+        <v>-85.45166015625</v>
       </c>
       <c r="X12" t="n">
-        <v>-63.8194580078125</v>
+        <v>-70.54534912109375</v>
       </c>
       <c r="Y12" t="n">
-        <v>-62.5792121887207</v>
+        <v>-81.03696441650391</v>
       </c>
       <c r="Z12" t="n">
-        <v>-61.20548248291016</v>
+        <v>-63.56891632080078</v>
       </c>
       <c r="AA12" t="n">
-        <v>-63.45474243164062</v>
+        <v>-74.08418273925781</v>
       </c>
       <c r="AB12" t="n">
-        <v>-69.09683227539062</v>
+        <v>-56.85927581787109</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>-42.83078384399414</v>
+        <v>-91.85797119140625</v>
       </c>
       <c r="B13" t="n">
-        <v>-44.63066482543945</v>
+        <v>-67.05140686035156</v>
       </c>
       <c r="C13" t="n">
-        <v>-45.1185417175293</v>
+        <v>-79.30532073974609</v>
       </c>
       <c r="D13" t="n">
-        <v>-46.47575759887695</v>
+        <v>-85.60809326171875</v>
       </c>
       <c r="E13" t="n">
-        <v>-48.03217315673828</v>
+        <v>-86.82609558105469</v>
       </c>
       <c r="F13" t="n">
-        <v>-49.4718132019043</v>
+        <v>-93.11331939697266</v>
       </c>
       <c r="G13" t="n">
-        <v>-51.05669403076172</v>
+        <v>-85.3387451171875</v>
       </c>
       <c r="H13" t="n">
-        <v>-50.10654067993164</v>
+        <v>-75.84977722167969</v>
       </c>
       <c r="I13" t="n">
-        <v>-51.26640701293945</v>
+        <v>-78.95613098144531</v>
       </c>
       <c r="J13" t="n">
-        <v>-51.29069900512695</v>
+        <v>-91.04914855957031</v>
       </c>
       <c r="K13" t="n">
-        <v>-47.90934753417969</v>
+        <v>-80.92641448974609</v>
       </c>
       <c r="L13" t="n">
-        <v>-49.36915969848633</v>
+        <v>-83.23627471923828</v>
       </c>
       <c r="M13" t="n">
-        <v>-48.53218841552734</v>
+        <v>-80.12120819091797</v>
       </c>
       <c r="N13" t="n">
-        <v>-51.71882247924805</v>
+        <v>-89.49805450439453</v>
       </c>
       <c r="O13" t="n">
-        <v>-56.48506546020508</v>
+        <v>-78.62351226806641</v>
       </c>
       <c r="P13" t="n">
-        <v>-60.19126129150391</v>
+        <v>-80.16453552246094</v>
       </c>
       <c r="Q13" t="n">
-        <v>-60.55670166015625</v>
+        <v>-84.93198394775391</v>
       </c>
       <c r="R13" t="n">
-        <v>-58.61617279052734</v>
+        <v>-85.26776885986328</v>
       </c>
       <c r="S13" t="n">
-        <v>-60.88991546630859</v>
+        <v>-88.83591461181641</v>
       </c>
       <c r="T13" t="n">
-        <v>-60.65923309326172</v>
+        <v>-74.87459564208984</v>
       </c>
       <c r="U13" t="n">
-        <v>-61.16953277587891</v>
+        <v>-81.71788787841797</v>
       </c>
       <c r="V13" t="n">
-        <v>-65.21192169189453</v>
+        <v>-86.89125823974609</v>
       </c>
       <c r="W13" t="n">
-        <v>-60.50817108154297</v>
+        <v>-84.08861541748047</v>
       </c>
       <c r="X13" t="n">
-        <v>-63.06206512451172</v>
+        <v>-80.40809631347656</v>
       </c>
       <c r="Y13" t="n">
-        <v>-59.16740798950195</v>
+        <v>-87.55194854736328</v>
       </c>
       <c r="Z13" t="n">
-        <v>-65.59519195556641</v>
+        <v>-77.14171600341797</v>
       </c>
       <c r="AA13" t="n">
-        <v>-62.58750534057617</v>
+        <v>-69.40772247314453</v>
       </c>
       <c r="AB13" t="n">
-        <v>-61.98289108276367</v>
+        <v>-60.48983001708984</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>-47.51673126220703</v>
+        <v>-81.52183532714844</v>
       </c>
       <c r="B14" t="n">
-        <v>-48.75061416625977</v>
+        <v>-57.5130500793457</v>
       </c>
       <c r="C14" t="n">
-        <v>-47.58793258666992</v>
+        <v>-83.07448577880859</v>
       </c>
       <c r="D14" t="n">
-        <v>-46.08667755126953</v>
+        <v>-70.50159454345703</v>
       </c>
       <c r="E14" t="n">
-        <v>-49.46879959106445</v>
+        <v>-81.10041046142578</v>
       </c>
       <c r="F14" t="n">
-        <v>-49.93172073364258</v>
+        <v>-51.62877655029297</v>
       </c>
       <c r="G14" t="n">
-        <v>-48.57807922363281</v>
+        <v>-85.46981048583984</v>
       </c>
       <c r="H14" t="n">
-        <v>-49.5107536315918</v>
+        <v>-71.06327819824219</v>
       </c>
       <c r="I14" t="n">
-        <v>-49.34942245483398</v>
+        <v>-81.03068542480469</v>
       </c>
       <c r="J14" t="n">
-        <v>-48.20915985107422</v>
+        <v>-69.96159362792969</v>
       </c>
       <c r="K14" t="n">
-        <v>-48.64847946166992</v>
+        <v>-80.61695861816406</v>
       </c>
       <c r="L14" t="n">
-        <v>-49.39806365966797</v>
+        <v>-73.20907592773438</v>
       </c>
       <c r="M14" t="n">
-        <v>-50.79407501220703</v>
+        <v>-88.35787200927734</v>
       </c>
       <c r="N14" t="n">
-        <v>-59.20371246337891</v>
+        <v>-58.25115203857422</v>
       </c>
       <c r="O14" t="n">
-        <v>-61.30499267578125</v>
+        <v>-75.60713958740234</v>
       </c>
       <c r="P14" t="n">
-        <v>-59.55078125</v>
+        <v>-56.98761749267578</v>
       </c>
       <c r="Q14" t="n">
-        <v>-59.24919891357422</v>
+        <v>-85.00205993652344</v>
       </c>
       <c r="R14" t="n">
-        <v>-63.20070266723633</v>
+        <v>-70.32524108886719</v>
       </c>
       <c r="S14" t="n">
-        <v>-64.11674499511719</v>
+        <v>-92.85805511474609</v>
       </c>
       <c r="T14" t="n">
-        <v>-64.63227844238281</v>
+        <v>-74.21308898925781</v>
       </c>
       <c r="U14" t="n">
-        <v>-61.22169876098633</v>
+        <v>-83.17790222167969</v>
       </c>
       <c r="V14" t="n">
-        <v>-58.41435623168945</v>
+        <v>-70.9168701171875</v>
       </c>
       <c r="W14" t="n">
-        <v>-62.36995697021484</v>
+        <v>-87.42076110839844</v>
       </c>
       <c r="X14" t="n">
-        <v>-63.6980094909668</v>
+        <v>-71.51743316650391</v>
       </c>
       <c r="Y14" t="n">
-        <v>-67.48525238037109</v>
+        <v>-75.40683746337891</v>
       </c>
       <c r="Z14" t="n">
-        <v>-65.1654052734375</v>
+        <v>-92.18955993652344</v>
       </c>
       <c r="AA14" t="n">
-        <v>-68.37232208251953</v>
+        <v>-72.42411041259766</v>
       </c>
       <c r="AB14" t="n">
-        <v>-56.7999153137207</v>
+        <v>-55.61881256103516</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>-62.85749053955078</v>
+        <v>-74.73738861083984</v>
       </c>
       <c r="B15" t="n">
-        <v>-58.91068649291992</v>
+        <v>-56.16622161865234</v>
       </c>
       <c r="C15" t="n">
-        <v>-60.86118316650391</v>
+        <v>-81.62152099609375</v>
       </c>
       <c r="D15" t="n">
-        <v>-55.72829055786133</v>
+        <v>-66.90846252441406</v>
       </c>
       <c r="E15" t="n">
-        <v>-57.48339080810547</v>
+        <v>-82.25130462646484</v>
       </c>
       <c r="F15" t="n">
-        <v>-58.85642623901367</v>
+        <v>-84.06909942626953</v>
       </c>
       <c r="G15" t="n">
-        <v>-58.8260612487793</v>
+        <v>-81.86180114746094</v>
       </c>
       <c r="H15" t="n">
-        <v>-58.48853302001953</v>
+        <v>-88.26759338378906</v>
       </c>
       <c r="I15" t="n">
-        <v>-60.32593536376953</v>
+        <v>-86.22010040283203</v>
       </c>
       <c r="J15" t="n">
-        <v>-59.03717803955078</v>
+        <v>-79.12225341796875</v>
       </c>
       <c r="K15" t="n">
-        <v>-56.71002960205078</v>
+        <v>-81.30608367919922</v>
       </c>
       <c r="L15" t="n">
-        <v>-62.59384918212891</v>
+        <v>-84.39495849609375</v>
       </c>
       <c r="M15" t="n">
-        <v>-63.90259552001953</v>
+        <v>-92.45939636230469</v>
       </c>
       <c r="N15" t="n">
-        <v>-64.41804504394531</v>
+        <v>-82.23694610595703</v>
       </c>
       <c r="O15" t="n">
-        <v>-69.18212127685547</v>
+        <v>-86.06368255615234</v>
       </c>
       <c r="P15" t="n">
-        <v>-65.32578277587891</v>
+        <v>-80.46586608886719</v>
       </c>
       <c r="Q15" t="n">
-        <v>-64.97996520996094</v>
+        <v>-81.94775390625</v>
       </c>
       <c r="R15" t="n">
-        <v>-68.59664916992188</v>
+        <v>-85.43621826171875</v>
       </c>
       <c r="S15" t="n">
-        <v>-64.74319458007812</v>
+        <v>-88.56216430664062</v>
       </c>
       <c r="T15" t="n">
-        <v>-67.94911193847656</v>
+        <v>-81.42649078369141</v>
       </c>
       <c r="U15" t="n">
-        <v>-68.52652740478516</v>
+        <v>-84.40409851074219</v>
       </c>
       <c r="V15" t="n">
-        <v>-68.61104583740234</v>
+        <v>-77.36714172363281</v>
       </c>
       <c r="W15" t="n">
-        <v>-67.33619689941406</v>
+        <v>-86.79314422607422</v>
       </c>
       <c r="X15" t="n">
-        <v>-69.02674865722656</v>
+        <v>-88.01502990722656</v>
       </c>
       <c r="Y15" t="n">
-        <v>-61.51787185668945</v>
+        <v>-88.91400909423828</v>
       </c>
       <c r="Z15" t="n">
-        <v>-68.82080841064453</v>
+        <v>-80.53227233886719</v>
       </c>
       <c r="AA15" t="n">
-        <v>-70.89997863769531</v>
+        <v>-69.99278259277344</v>
       </c>
       <c r="AB15" t="n">
-        <v>-68.82781219482422</v>
+        <v>-69.79730987548828</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>-56.38846588134766</v>
+        <v>-67.52352142333984</v>
       </c>
       <c r="B16" t="n">
-        <v>-57.34038162231445</v>
+        <v>-64.98625946044922</v>
       </c>
       <c r="C16" t="n">
-        <v>-62.07413482666016</v>
+        <v>-94.30577087402344</v>
       </c>
       <c r="D16" t="n">
-        <v>-60.6699333190918</v>
+        <v>-70.56499481201172</v>
       </c>
       <c r="E16" t="n">
-        <v>-63.1342887878418</v>
+        <v>-77.49476623535156</v>
       </c>
       <c r="F16" t="n">
-        <v>-55.47884368896484</v>
+        <v>-66.02000427246094</v>
       </c>
       <c r="G16" t="n">
-        <v>-59.83060836791992</v>
+        <v>-87.79641723632812</v>
       </c>
       <c r="H16" t="n">
-        <v>-61.33960723876953</v>
+        <v>-60.07273101806641</v>
       </c>
       <c r="I16" t="n">
-        <v>-63.48603057861328</v>
+        <v>-88.72845458984375</v>
       </c>
       <c r="J16" t="n">
-        <v>-60.2646484375</v>
+        <v>-58.47612762451172</v>
       </c>
       <c r="K16" t="n">
-        <v>-60.72742462158203</v>
+        <v>-86.21176910400391</v>
       </c>
       <c r="L16" t="n">
-        <v>-63.84701538085938</v>
+        <v>-59.94593048095703</v>
       </c>
       <c r="M16" t="n">
-        <v>-60.87076950073242</v>
+        <v>-79.930419921875</v>
       </c>
       <c r="N16" t="n">
-        <v>-62.70367431640625</v>
+        <v>-70.39402008056641</v>
       </c>
       <c r="O16" t="n">
-        <v>-71.03031158447266</v>
+        <v>-80.33487701416016</v>
       </c>
       <c r="P16" t="n">
-        <v>-68.57252502441406</v>
+        <v>-62.94446563720703</v>
       </c>
       <c r="Q16" t="n">
-        <v>-68.17038726806641</v>
+        <v>-84.02306365966797</v>
       </c>
       <c r="R16" t="n">
-        <v>-70.06791687011719</v>
+        <v>-68.17873382568359</v>
       </c>
       <c r="S16" t="n">
-        <v>-64.652587890625</v>
+        <v>-85.04652404785156</v>
       </c>
       <c r="T16" t="n">
-        <v>-66.68198394775391</v>
+        <v>-74.17673492431641</v>
       </c>
       <c r="U16" t="n">
-        <v>-68.19805908203125</v>
+        <v>-74.09182739257812</v>
       </c>
       <c r="V16" t="n">
-        <v>-69.00946807861328</v>
+        <v>-59.77641677856445</v>
       </c>
       <c r="W16" t="n">
-        <v>-66.61112213134766</v>
+        <v>-92.39060974121094</v>
       </c>
       <c r="X16" t="n">
-        <v>-68.23643493652344</v>
+        <v>-74.36931610107422</v>
       </c>
       <c r="Y16" t="n">
-        <v>-70.89073181152344</v>
+        <v>-88.37191009521484</v>
       </c>
       <c r="Z16" t="n">
-        <v>-69.98703765869141</v>
+        <v>-61.69705963134766</v>
       </c>
       <c r="AA16" t="n">
-        <v>-68.46490478515625</v>
+        <v>-68.73951721191406</v>
       </c>
       <c r="AB16" t="n">
-        <v>-69.23457336425781</v>
+        <v>-68.94086456298828</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>-59.42267608642578</v>
+        <v>-86.19416046142578</v>
       </c>
       <c r="B17" t="n">
-        <v>-59.13381958007812</v>
+        <v>-88.07676696777344</v>
       </c>
       <c r="C17" t="n">
-        <v>-63.7338981628418</v>
+        <v>-89.109619140625</v>
       </c>
       <c r="D17" t="n">
-        <v>-61.96198272705078</v>
+        <v>-69.98096466064453</v>
       </c>
       <c r="E17" t="n">
-        <v>-61.41206741333008</v>
+        <v>-83.45527648925781</v>
       </c>
       <c r="F17" t="n">
-        <v>-60.87737274169922</v>
+        <v>-83.68931579589844</v>
       </c>
       <c r="G17" t="n">
-        <v>-60.70981597900391</v>
+        <v>-85.88021850585938</v>
       </c>
       <c r="H17" t="n">
-        <v>-58.98241424560547</v>
+        <v>-75.29580688476562</v>
       </c>
       <c r="I17" t="n">
-        <v>-58.94135665893555</v>
+        <v>-91.52179718017578</v>
       </c>
       <c r="J17" t="n">
-        <v>-55.0152473449707</v>
+        <v>-92.86940002441406</v>
       </c>
       <c r="K17" t="n">
-        <v>-59.26693725585938</v>
+        <v>-79.77114868164062</v>
       </c>
       <c r="L17" t="n">
-        <v>-62.57771682739258</v>
+        <v>-84.40177917480469</v>
       </c>
       <c r="M17" t="n">
-        <v>-63.30551147460938</v>
+        <v>-78.59423828125</v>
       </c>
       <c r="N17" t="n">
-        <v>-63.8235969543457</v>
+        <v>-76.25550842285156</v>
       </c>
       <c r="O17" t="n">
-        <v>-72.58164978027344</v>
+        <v>-81.31032562255859</v>
       </c>
       <c r="P17" t="n">
-        <v>-71.88575744628906</v>
+        <v>-83.55587005615234</v>
       </c>
       <c r="Q17" t="n">
-        <v>-70.93521881103516</v>
+        <v>-96.93504333496094</v>
       </c>
       <c r="R17" t="n">
-        <v>-67.06650543212891</v>
+        <v>-86.43873596191406</v>
       </c>
       <c r="S17" t="n">
-        <v>-69.34379577636719</v>
+        <v>-76.68190002441406</v>
       </c>
       <c r="T17" t="n">
-        <v>-65.62214660644531</v>
+        <v>-88.95093536376953</v>
       </c>
       <c r="U17" t="n">
-        <v>-62.95893096923828</v>
+        <v>-81.66493225097656</v>
       </c>
       <c r="V17" t="n">
-        <v>-70.72054290771484</v>
+        <v>-81.21434020996094</v>
       </c>
       <c r="W17" t="n">
-        <v>-67.04502868652344</v>
+        <v>-98.22145080566406</v>
       </c>
       <c r="X17" t="n">
-        <v>-69.67881011962891</v>
+        <v>-79.34330749511719</v>
       </c>
       <c r="Y17" t="n">
-        <v>-68.98995971679688</v>
+        <v>-70.42747497558594</v>
       </c>
       <c r="Z17" t="n">
-        <v>-72.06125640869141</v>
+        <v>-77.76503753662109</v>
       </c>
       <c r="AA17" t="n">
-        <v>-67.27046203613281</v>
+        <v>-67.53319549560547</v>
       </c>
       <c r="AB17" t="n">
-        <v>-71.66034698486328</v>
+        <v>-74.71469879150391</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>-61.83106231689453</v>
+        <v>-82.62165832519531</v>
       </c>
       <c r="B18" t="n">
-        <v>-57.2940788269043</v>
+        <v>-43.41449737548828</v>
       </c>
       <c r="C18" t="n">
-        <v>-57.56439208984375</v>
+        <v>-71.38314056396484</v>
       </c>
       <c r="D18" t="n">
-        <v>-59.26872634887695</v>
+        <v>-66.42324829101562</v>
       </c>
       <c r="E18" t="n">
-        <v>-60.31586837768555</v>
+        <v>-84.23762512207031</v>
       </c>
       <c r="F18" t="n">
-        <v>-57.85989379882812</v>
+        <v>-75.84324645996094</v>
       </c>
       <c r="G18" t="n">
-        <v>-60.2921028137207</v>
+        <v>-84.23597717285156</v>
       </c>
       <c r="H18" t="n">
-        <v>-63.25429534912109</v>
+        <v>-66.85299682617188</v>
       </c>
       <c r="I18" t="n">
-        <v>-60.44903564453125</v>
+        <v>-69.86741638183594</v>
       </c>
       <c r="J18" t="n">
-        <v>-58.1170654296875</v>
+        <v>-60.14487457275391</v>
       </c>
       <c r="K18" t="n">
-        <v>-63.55496978759766</v>
+        <v>-89.94473266601562</v>
       </c>
       <c r="L18" t="n">
-        <v>-61.96519088745117</v>
+        <v>-70.40461730957031</v>
       </c>
       <c r="M18" t="n">
-        <v>-65.33879089355469</v>
+        <v>-82.48385620117188</v>
       </c>
       <c r="N18" t="n">
-        <v>-64.08265686035156</v>
+        <v>-65.6663818359375</v>
       </c>
       <c r="O18" t="n">
-        <v>-72.75587463378906</v>
+        <v>-77.67500305175781</v>
       </c>
       <c r="P18" t="n">
-        <v>-74.13695526123047</v>
+        <v>-60.53350830078125</v>
       </c>
       <c r="Q18" t="n">
-        <v>-71.93818664550781</v>
+        <v>-79.69316101074219</v>
       </c>
       <c r="R18" t="n">
-        <v>-68.91413879394531</v>
+        <v>-65.67733001708984</v>
       </c>
       <c r="S18" t="n">
-        <v>-67.83354187011719</v>
+        <v>-90.74700164794922</v>
       </c>
       <c r="T18" t="n">
-        <v>-70.50760650634766</v>
+        <v>-59.31285858154297</v>
       </c>
       <c r="U18" t="n">
-        <v>-65.79615783691406</v>
+        <v>-87.57405090332031</v>
       </c>
       <c r="V18" t="n">
-        <v>-65.18762969970703</v>
+        <v>-60.87296295166016</v>
       </c>
       <c r="W18" t="n">
-        <v>-66.85182952880859</v>
+        <v>-88.87261962890625</v>
       </c>
       <c r="X18" t="n">
-        <v>-73.29057312011719</v>
+        <v>-63.21992874145508</v>
       </c>
       <c r="Y18" t="n">
-        <v>-69.37008666992188</v>
+        <v>-85.0941162109375</v>
       </c>
       <c r="Z18" t="n">
-        <v>-67.69587707519531</v>
+        <v>-66.10830688476562</v>
       </c>
       <c r="AA18" t="n">
-        <v>-68.67643737792969</v>
+        <v>-84.77953338623047</v>
       </c>
       <c r="AB18" t="n">
-        <v>-68.58973693847656</v>
+        <v>-66.55311584472656</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>-60.22237396240234</v>
+        <v>-76.17449951171875</v>
       </c>
       <c r="B19" t="n">
-        <v>-63.47686767578125</v>
+        <v>-67.013916015625</v>
       </c>
       <c r="C19" t="n">
-        <v>-59.06822967529297</v>
+        <v>-74.81755065917969</v>
       </c>
       <c r="D19" t="n">
-        <v>-59.99626541137695</v>
+        <v>-71.03774261474609</v>
       </c>
       <c r="E19" t="n">
-        <v>-65.02643585205078</v>
+        <v>-77.64113616943359</v>
       </c>
       <c r="F19" t="n">
-        <v>-62.54187774658203</v>
+        <v>-92.07009887695312</v>
       </c>
       <c r="G19" t="n">
-        <v>-58.93321990966797</v>
+        <v>-96.84278869628906</v>
       </c>
       <c r="H19" t="n">
-        <v>-57.83332061767578</v>
+        <v>-89.4951171875</v>
       </c>
       <c r="I19" t="n">
-        <v>-63.82882690429688</v>
+        <v>-89.9361572265625</v>
       </c>
       <c r="J19" t="n">
-        <v>-57.41638946533203</v>
+        <v>-75.00746154785156</v>
       </c>
       <c r="K19" t="n">
-        <v>-62.21553802490234</v>
+        <v>-97.78981781005859</v>
       </c>
       <c r="L19" t="n">
-        <v>-63.37518310546875</v>
+        <v>-84.31363677978516</v>
       </c>
       <c r="M19" t="n">
-        <v>-64.72939300537109</v>
+        <v>-85.64580535888672</v>
       </c>
       <c r="N19" t="n">
-        <v>-62.16261672973633</v>
+        <v>-85.54198455810547</v>
       </c>
       <c r="O19" t="n">
-        <v>-71.41374206542969</v>
+        <v>-87.25136566162109</v>
       </c>
       <c r="P19" t="n">
-        <v>-74.47224426269531</v>
+        <v>-82.82496643066406</v>
       </c>
       <c r="Q19" t="n">
-        <v>-70.22853851318359</v>
+        <v>-78.21230316162109</v>
       </c>
       <c r="R19" t="n">
-        <v>-72.87565612792969</v>
+        <v>-77.97665405273438</v>
       </c>
       <c r="S19" t="n">
-        <v>-69.39543914794922</v>
+        <v>-79.92378997802734</v>
       </c>
       <c r="T19" t="n">
-        <v>-68.6318359375</v>
+        <v>-84.60964202880859</v>
       </c>
       <c r="U19" t="n">
-        <v>-66.46939086914062</v>
+        <v>-87.28901672363281</v>
       </c>
       <c r="V19" t="n">
-        <v>-67.54111480712891</v>
+        <v>-89.64656829833984</v>
       </c>
       <c r="W19" t="n">
-        <v>-68.49770355224609</v>
+        <v>-70.54649353027344</v>
       </c>
       <c r="X19" t="n">
-        <v>-66.66084289550781</v>
+        <v>-82.74041748046875</v>
       </c>
       <c r="Y19" t="n">
-        <v>-69.35010528564453</v>
+        <v>-86.70389556884766</v>
       </c>
       <c r="Z19" t="n">
-        <v>-70.63454437255859</v>
+        <v>-68.07913208007812</v>
       </c>
       <c r="AA19" t="n">
-        <v>-69.20323181152344</v>
+        <v>-66.73598480224609</v>
       </c>
       <c r="AB19" t="n">
-        <v>-70.41865539550781</v>
+        <v>-71.23011779785156</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>-59.28575897216797</v>
+        <v>-80.03559112548828</v>
       </c>
       <c r="B20" t="n">
-        <v>-61.65962982177734</v>
+        <v>-43.18878936767578</v>
       </c>
       <c r="C20" t="n">
-        <v>-63.07477951049805</v>
+        <v>-78.69696807861328</v>
       </c>
       <c r="D20" t="n">
-        <v>-62.88108062744141</v>
+        <v>-66.55899810791016</v>
       </c>
       <c r="E20" t="n">
-        <v>-60.58463287353516</v>
+        <v>-87.63697814941406</v>
       </c>
       <c r="F20" t="n">
-        <v>-63.15989303588867</v>
+        <v>-67.87431335449219</v>
       </c>
       <c r="G20" t="n">
-        <v>-58.39110565185547</v>
+        <v>-64.97301483154297</v>
       </c>
       <c r="H20" t="n">
-        <v>-63.98485565185547</v>
+        <v>-50.48641204833984</v>
       </c>
       <c r="I20" t="n">
-        <v>-62.8541259765625</v>
+        <v>-89.41603851318359</v>
       </c>
       <c r="J20" t="n">
-        <v>-57.34558868408203</v>
+        <v>-85.44052886962891</v>
       </c>
       <c r="K20" t="n">
-        <v>-62.91143798828125</v>
+        <v>-83.82162475585938</v>
       </c>
       <c r="L20" t="n">
-        <v>-59.20075225830078</v>
+        <v>-84.11287689208984</v>
       </c>
       <c r="M20" t="n">
-        <v>-62.87678909301758</v>
+        <v>-86.27117156982422</v>
       </c>
       <c r="N20" t="n">
-        <v>-64.90455627441406</v>
+        <v>-69.71119689941406</v>
       </c>
       <c r="O20" t="n">
-        <v>-72.75055694580078</v>
+        <v>-84.28071594238281</v>
       </c>
       <c r="P20" t="n">
-        <v>-71.33747100830078</v>
+        <v>-84.59843444824219</v>
       </c>
       <c r="Q20" t="n">
-        <v>-72.53404235839844</v>
+        <v>-93.96681213378906</v>
       </c>
       <c r="R20" t="n">
-        <v>-73.54200744628906</v>
+        <v>-65.81754302978516</v>
       </c>
       <c r="S20" t="n">
-        <v>-70.74726867675781</v>
+        <v>-85.40354156494141</v>
       </c>
       <c r="T20" t="n">
-        <v>-74.00025939941406</v>
+        <v>-59.75896453857422</v>
       </c>
       <c r="U20" t="n">
-        <v>-67.48317718505859</v>
+        <v>-87.40631866455078</v>
       </c>
       <c r="V20" t="n">
-        <v>-68.86760711669922</v>
+        <v>-73.46316528320312</v>
       </c>
       <c r="W20" t="n">
-        <v>-69.27426910400391</v>
+        <v>-91.22660064697266</v>
       </c>
       <c r="X20" t="n">
-        <v>-66.63710021972656</v>
+        <v>-62.51685333251953</v>
       </c>
       <c r="Y20" t="n">
-        <v>-63.05976104736328</v>
+        <v>-84.33611297607422</v>
       </c>
       <c r="Z20" t="n">
-        <v>-65.94407653808594</v>
+        <v>-68.87302398681641</v>
       </c>
       <c r="AA20" t="n">
-        <v>-68.19731903076172</v>
+        <v>-72.57402038574219</v>
       </c>
       <c r="AB20" t="n">
-        <v>-71.98754119873047</v>
+        <v>-63.47971343994141</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>-63.02155685424805</v>
+        <v>-83.83476257324219</v>
       </c>
       <c r="B21" t="n">
-        <v>-57.57272338867188</v>
+        <v>-77.65038299560547</v>
       </c>
       <c r="C21" t="n">
-        <v>-63.90592193603516</v>
+        <v>-93.21830749511719</v>
       </c>
       <c r="D21" t="n">
-        <v>-59.77408981323242</v>
+        <v>-66.30276489257812</v>
       </c>
       <c r="E21" t="n">
-        <v>-58.2033805847168</v>
+        <v>-94.18461608886719</v>
       </c>
       <c r="F21" t="n">
-        <v>-64.89002227783203</v>
+        <v>-77.16870880126953</v>
       </c>
       <c r="G21" t="n">
-        <v>-67.40718841552734</v>
+        <v>-82.0250244140625</v>
       </c>
       <c r="H21" t="n">
-        <v>-58.28169631958008</v>
+        <v>-82.04768371582031</v>
       </c>
       <c r="I21" t="n">
-        <v>-66.31156158447266</v>
+        <v>-78.63764190673828</v>
       </c>
       <c r="J21" t="n">
-        <v>-60.58335113525391</v>
+        <v>-82.84593200683594</v>
       </c>
       <c r="K21" t="n">
-        <v>-64.80155944824219</v>
+        <v>-78.73563385009766</v>
       </c>
       <c r="L21" t="n">
-        <v>-60.7827262878418</v>
+        <v>-87.28581237792969</v>
       </c>
       <c r="M21" t="n">
-        <v>-66.63515472412109</v>
+        <v>-89.39503479003906</v>
       </c>
       <c r="N21" t="n">
-        <v>-63.49749755859375</v>
+        <v>-74.42645263671875</v>
       </c>
       <c r="O21" t="n">
-        <v>-73.27021026611328</v>
+        <v>-84.94984436035156</v>
       </c>
       <c r="P21" t="n">
-        <v>-69.54164123535156</v>
+        <v>-81.5509033203125</v>
       </c>
       <c r="Q21" t="n">
-        <v>-74.62611389160156</v>
+        <v>-86.85988616943359</v>
       </c>
       <c r="R21" t="n">
-        <v>-73.64181518554688</v>
+        <v>-77.99694061279297</v>
       </c>
       <c r="S21" t="n">
-        <v>-69.92765808105469</v>
+        <v>-91.58736419677734</v>
       </c>
       <c r="T21" t="n">
-        <v>-75.22490692138672</v>
+        <v>-81.04975891113281</v>
       </c>
       <c r="U21" t="n">
-        <v>-70.1226806640625</v>
+        <v>-89.71036529541016</v>
       </c>
       <c r="V21" t="n">
-        <v>-67.55543518066406</v>
+        <v>-75.09027862548828</v>
       </c>
       <c r="W21" t="n">
-        <v>-66.85188293457031</v>
+        <v>-91.29274749755859</v>
       </c>
       <c r="X21" t="n">
-        <v>-68.68582916259766</v>
+        <v>-86.89338684082031</v>
       </c>
       <c r="Y21" t="n">
-        <v>-68.08729553222656</v>
+        <v>-87.54954528808594</v>
       </c>
       <c r="Z21" t="n">
-        <v>-70.24665069580078</v>
+        <v>-73.27352905273438</v>
       </c>
       <c r="AA21" t="n">
-        <v>-71.38810729980469</v>
+        <v>-64.31504821777344</v>
       </c>
       <c r="AB21" t="n">
-        <v>-66.99993133544922</v>
+        <v>-67.67134094238281</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>-58.43603515625</v>
+        <v>-81.47010040283203</v>
       </c>
       <c r="B22" t="n">
-        <v>-63.3401985168457</v>
+        <v>-59.60482788085938</v>
       </c>
       <c r="C22" t="n">
-        <v>-58.90224075317383</v>
+        <v>-94.48636627197266</v>
       </c>
       <c r="D22" t="n">
-        <v>-66.59515380859375</v>
+        <v>-50.64267730712891</v>
       </c>
       <c r="E22" t="n">
-        <v>-63.80620574951172</v>
+        <v>-78.24794006347656</v>
       </c>
       <c r="F22" t="n">
-        <v>-64.86911773681641</v>
+        <v>-63.6650276184082</v>
       </c>
       <c r="G22" t="n">
-        <v>-63.97324371337891</v>
+        <v>-73.45377349853516</v>
       </c>
       <c r="H22" t="n">
-        <v>-61.1937255859375</v>
+        <v>-57.27678298950195</v>
       </c>
       <c r="I22" t="n">
-        <v>-64.47359466552734</v>
+        <v>-89.50059509277344</v>
       </c>
       <c r="J22" t="n">
-        <v>-64.29080963134766</v>
+        <v>-82.46440124511719</v>
       </c>
       <c r="K22" t="n">
-        <v>-65.61241912841797</v>
+        <v>-88.21720886230469</v>
       </c>
       <c r="L22" t="n">
-        <v>-65.59532928466797</v>
+        <v>-74.49563598632812</v>
       </c>
       <c r="M22" t="n">
-        <v>-61.87969970703125</v>
+        <v>-76.92356109619141</v>
       </c>
       <c r="N22" t="n">
-        <v>-65.51930236816406</v>
+        <v>-62.88359832763672</v>
       </c>
       <c r="O22" t="n">
-        <v>-75.40399169921875</v>
+        <v>-77.31114196777344</v>
       </c>
       <c r="P22" t="n">
-        <v>-70.70539093017578</v>
+        <v>-72.74290466308594</v>
       </c>
       <c r="Q22" t="n">
-        <v>-73.70855712890625</v>
+        <v>-85.79988861083984</v>
       </c>
       <c r="R22" t="n">
-        <v>-73.6514892578125</v>
+        <v>-59.2306022644043</v>
       </c>
       <c r="S22" t="n">
-        <v>-72.99858093261719</v>
+        <v>-84.46848297119141</v>
       </c>
       <c r="T22" t="n">
-        <v>-69.170166015625</v>
+        <v>-64.44054412841797</v>
       </c>
       <c r="U22" t="n">
-        <v>-73.95167541503906</v>
+        <v>-78.62225341796875</v>
       </c>
       <c r="V22" t="n">
-        <v>-75.86332702636719</v>
+        <v>-64.17247772216797</v>
       </c>
       <c r="W22" t="n">
-        <v>-69.43092346191406</v>
+        <v>-92.98152160644531</v>
       </c>
       <c r="X22" t="n">
-        <v>-67.06025695800781</v>
+        <v>-67.05293273925781</v>
       </c>
       <c r="Y22" t="n">
-        <v>-70.66634368896484</v>
+        <v>-84.73471069335938</v>
       </c>
       <c r="Z22" t="n">
-        <v>-66.25499725341797</v>
+        <v>-72.03256225585938</v>
       </c>
       <c r="AA22" t="n">
-        <v>-68.08611297607422</v>
+        <v>-87.57431030273438</v>
       </c>
       <c r="AB22" t="n">
-        <v>-73.39205932617188</v>
+        <v>-52.27480316162109</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>-62.31946563720703</v>
+        <v>-76.79166412353516</v>
       </c>
       <c r="B23" t="n">
-        <v>-61.56635665893555</v>
+        <v>-77.76380920410156</v>
       </c>
       <c r="C23" t="n">
-        <v>-62.89469146728516</v>
+        <v>-82.16595458984375</v>
       </c>
       <c r="D23" t="n">
-        <v>-59.70127105712891</v>
+        <v>-88.71527862548828</v>
       </c>
       <c r="E23" t="n">
-        <v>-64.22630310058594</v>
+        <v>-86.80323028564453</v>
       </c>
       <c r="F23" t="n">
-        <v>-60.70556640625</v>
+        <v>-89.66893005371094</v>
       </c>
       <c r="G23" t="n">
-        <v>-60.27272415161133</v>
+        <v>-75.66677093505859</v>
       </c>
       <c r="H23" t="n">
-        <v>-62.30795288085938</v>
+        <v>-67.35118103027344</v>
       </c>
       <c r="I23" t="n">
-        <v>-63.61611938476562</v>
+        <v>-84.60117340087891</v>
       </c>
       <c r="J23" t="n">
-        <v>-59.17644119262695</v>
+        <v>-85.22383880615234</v>
       </c>
       <c r="K23" t="n">
-        <v>-63.3682746887207</v>
+        <v>-88.62422180175781</v>
       </c>
       <c r="L23" t="n">
-        <v>-65.74026489257812</v>
+        <v>-80.18705749511719</v>
       </c>
       <c r="M23" t="n">
-        <v>-66.40638732910156</v>
+        <v>-88.63742828369141</v>
       </c>
       <c r="N23" t="n">
-        <v>-65.28287506103516</v>
+        <v>-94.03144836425781</v>
       </c>
       <c r="O23" t="n">
-        <v>-69.89405822753906</v>
+        <v>-81.89837646484375</v>
       </c>
       <c r="P23" t="n">
-        <v>-69.23571014404297</v>
+        <v>-72.66184234619141</v>
       </c>
       <c r="Q23" t="n">
-        <v>-68.48847198486328</v>
+        <v>-86.37766265869141</v>
       </c>
       <c r="R23" t="n">
-        <v>-76.57027435302734</v>
+        <v>-84.09983825683594</v>
       </c>
       <c r="S23" t="n">
-        <v>-69.45835876464844</v>
+        <v>-79.15499877929688</v>
       </c>
       <c r="T23" t="n">
-        <v>-73.80234527587891</v>
+        <v>-86.69511413574219</v>
       </c>
       <c r="U23" t="n">
-        <v>-70.62435150146484</v>
+        <v>-79.85305786132812</v>
       </c>
       <c r="V23" t="n">
-        <v>-71.26240539550781</v>
+        <v>-83.61514282226562</v>
       </c>
       <c r="W23" t="n">
-        <v>-67.50424194335938</v>
+        <v>-88.22004699707031</v>
       </c>
       <c r="X23" t="n">
-        <v>-70.24421691894531</v>
+        <v>-94.46286773681641</v>
       </c>
       <c r="Y23" t="n">
-        <v>-68.94863128662109</v>
+        <v>-86.52433776855469</v>
       </c>
       <c r="Z23" t="n">
-        <v>-69.54975891113281</v>
+        <v>-79.67662048339844</v>
       </c>
       <c r="AA23" t="n">
-        <v>-68.30074310302734</v>
+        <v>-70.08498382568359</v>
       </c>
       <c r="AB23" t="n">
-        <v>-67.47600555419922</v>
+        <v>-59.38927459716797</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>-57.67850875854492</v>
+        <v>-68.27345275878906</v>
       </c>
       <c r="B24" t="n">
-        <v>-62.32958221435547</v>
+        <v>-54.63493728637695</v>
       </c>
       <c r="C24" t="n">
-        <v>-62.97943878173828</v>
+        <v>-90.19269561767578</v>
       </c>
       <c r="D24" t="n">
-        <v>-61.75990676879883</v>
+        <v>-62.8836784362793</v>
       </c>
       <c r="E24" t="n">
-        <v>-61.54686737060547</v>
+        <v>-91.60740661621094</v>
       </c>
       <c r="F24" t="n">
-        <v>-60.72644805908203</v>
+        <v>-69.21094512939453</v>
       </c>
       <c r="G24" t="n">
-        <v>-62.08292770385742</v>
+        <v>-85.58144378662109</v>
       </c>
       <c r="H24" t="n">
-        <v>-66.03944396972656</v>
+        <v>-46.80667877197266</v>
       </c>
       <c r="I24" t="n">
-        <v>-65.76832580566406</v>
+        <v>-72.62825012207031</v>
       </c>
       <c r="J24" t="n">
-        <v>-58.81687164306641</v>
+        <v>-62.3961181640625</v>
       </c>
       <c r="K24" t="n">
-        <v>-58.85013961791992</v>
+        <v>-66.99666595458984</v>
       </c>
       <c r="L24" t="n">
-        <v>-61.44649124145508</v>
+        <v>-69.25620269775391</v>
       </c>
       <c r="M24" t="n">
-        <v>-62.07324981689453</v>
+        <v>-75.67399597167969</v>
       </c>
       <c r="N24" t="n">
-        <v>-67.30184936523438</v>
+        <v>-76.64339447021484</v>
       </c>
       <c r="O24" t="n">
-        <v>-71.75321960449219</v>
+        <v>-83.86566925048828</v>
       </c>
       <c r="P24" t="n">
-        <v>-70.87507629394531</v>
+        <v>-55.00302124023438</v>
       </c>
       <c r="Q24" t="n">
-        <v>-72.97957611083984</v>
+        <v>-83.97892761230469</v>
       </c>
       <c r="R24" t="n">
-        <v>-70.14607238769531</v>
+        <v>-68.31809997558594</v>
       </c>
       <c r="S24" t="n">
-        <v>-72.2069091796875</v>
+        <v>-92.40208435058594</v>
       </c>
       <c r="T24" t="n">
-        <v>-72.02680969238281</v>
+        <v>-68.79983520507812</v>
       </c>
       <c r="U24" t="n">
-        <v>-72.50333404541016</v>
+        <v>-83.35289764404297</v>
       </c>
       <c r="V24" t="n">
-        <v>-72.33637237548828</v>
+        <v>-78.23310852050781</v>
       </c>
       <c r="W24" t="n">
-        <v>-73.71463775634766</v>
+        <v>-86.49110412597656</v>
       </c>
       <c r="X24" t="n">
-        <v>-70.89423370361328</v>
+        <v>-73.066162109375</v>
       </c>
       <c r="Y24" t="n">
-        <v>-68.66084289550781</v>
+        <v>-90.06870269775391</v>
       </c>
       <c r="Z24" t="n">
-        <v>-70.59306335449219</v>
+        <v>-70.71073150634766</v>
       </c>
       <c r="AA24" t="n">
-        <v>-71.14217376708984</v>
+        <v>-78.94245147705078</v>
       </c>
       <c r="AB24" t="n">
-        <v>-70.23805236816406</v>
+        <v>-67.70758819580078</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>-69.84353637695312</v>
+        <v>-87.66344451904297</v>
       </c>
       <c r="B25" t="n">
-        <v>-60.43085479736328</v>
+        <v>-71.01197052001953</v>
       </c>
       <c r="C25" t="n">
-        <v>-60.4083137512207</v>
+        <v>-75.92289733886719</v>
       </c>
       <c r="D25" t="n">
-        <v>-65.89048767089844</v>
+        <v>-76.14515686035156</v>
       </c>
       <c r="E25" t="n">
-        <v>-62.44992828369141</v>
+        <v>-86.67536926269531</v>
       </c>
       <c r="F25" t="n">
-        <v>-60.8406982421875</v>
+        <v>-74.12678527832031</v>
       </c>
       <c r="G25" t="n">
-        <v>-59.87204742431641</v>
+        <v>-81.97611999511719</v>
       </c>
       <c r="H25" t="n">
-        <v>-62.60335159301758</v>
+        <v>-68.11188507080078</v>
       </c>
       <c r="I25" t="n">
-        <v>-69.03076171875</v>
+        <v>-88.02799987792969</v>
       </c>
       <c r="J25" t="n">
-        <v>-58.3480110168457</v>
+        <v>-77.43516540527344</v>
       </c>
       <c r="K25" t="n">
-        <v>-61.72037506103516</v>
+        <v>-95.23427581787109</v>
       </c>
       <c r="L25" t="n">
-        <v>-59.91162872314453</v>
+        <v>-71.348876953125</v>
       </c>
       <c r="M25" t="n">
-        <v>-64.50089263916016</v>
+        <v>-83.02712249755859</v>
       </c>
       <c r="N25" t="n">
-        <v>-62.01755523681641</v>
+        <v>-79.24481201171875</v>
       </c>
       <c r="O25" t="n">
-        <v>-69.37085723876953</v>
+        <v>-83.74098968505859</v>
       </c>
       <c r="P25" t="n">
-        <v>-71.45938110351562</v>
+        <v>-71.73258972167969</v>
       </c>
       <c r="Q25" t="n">
-        <v>-72.78197479248047</v>
+        <v>-84.50163269042969</v>
       </c>
       <c r="R25" t="n">
-        <v>-72.18806457519531</v>
+        <v>-86.75232696533203</v>
       </c>
       <c r="S25" t="n">
-        <v>-68.00881195068359</v>
+        <v>-93.14303588867188</v>
       </c>
       <c r="T25" t="n">
-        <v>-71.77848052978516</v>
+        <v>-69.50263977050781</v>
       </c>
       <c r="U25" t="n">
-        <v>-69.82856750488281</v>
+        <v>-78.54885864257812</v>
       </c>
       <c r="V25" t="n">
-        <v>-73.36096954345703</v>
+        <v>-60.4672966003418</v>
       </c>
       <c r="W25" t="n">
-        <v>-77.06751251220703</v>
+        <v>-80.68369293212891</v>
       </c>
       <c r="X25" t="n">
-        <v>-72.18520355224609</v>
+        <v>-86.65901947021484</v>
       </c>
       <c r="Y25" t="n">
-        <v>-72.07591247558594</v>
+        <v>-71.34713745117188</v>
       </c>
       <c r="Z25" t="n">
-        <v>-71.1160888671875</v>
+        <v>-69.05567932128906</v>
       </c>
       <c r="AA25" t="n">
-        <v>-70.2421875</v>
+        <v>-59.09284591674805</v>
       </c>
       <c r="AB25" t="n">
-        <v>-67.95124053955078</v>
+        <v>-70.14827728271484</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>-61.78984451293945</v>
+        <v>-86.44258880615234</v>
       </c>
       <c r="B26" t="n">
-        <v>-63.07132720947266</v>
+        <v>-52.38562774658203</v>
       </c>
       <c r="C26" t="n">
-        <v>-65.62767791748047</v>
+        <v>-74.73411560058594</v>
       </c>
       <c r="D26" t="n">
-        <v>-64.64341735839844</v>
+        <v>-67.68563842773438</v>
       </c>
       <c r="E26" t="n">
-        <v>-64.85856628417969</v>
+        <v>-68.0035400390625</v>
       </c>
       <c r="F26" t="n">
-        <v>-64.02691650390625</v>
+        <v>-62.79915237426758</v>
       </c>
       <c r="G26" t="n">
-        <v>-59.75116729736328</v>
+        <v>-68.83484649658203</v>
       </c>
       <c r="H26" t="n">
-        <v>-65.12395477294922</v>
+        <v>-77.06877136230469</v>
       </c>
       <c r="I26" t="n">
-        <v>-63.06182861328125</v>
+        <v>-71.05961608886719</v>
       </c>
       <c r="J26" t="n">
-        <v>-62.03315353393555</v>
+        <v>-55.87485504150391</v>
       </c>
       <c r="K26" t="n">
-        <v>-62.52146148681641</v>
+        <v>-67.39602661132812</v>
       </c>
       <c r="L26" t="n">
-        <v>-61.95294952392578</v>
+        <v>-63.00986480712891</v>
       </c>
       <c r="M26" t="n">
-        <v>-63.04364776611328</v>
+        <v>-68.83013916015625</v>
       </c>
       <c r="N26" t="n">
-        <v>-63.49364471435547</v>
+        <v>-48.32035064697266</v>
       </c>
       <c r="O26" t="n">
-        <v>-76.49517822265625</v>
+        <v>-73.48889923095703</v>
       </c>
       <c r="P26" t="n">
-        <v>-72.51955413818359</v>
+        <v>-75.27336883544922</v>
       </c>
       <c r="Q26" t="n">
-        <v>-72.7210693359375</v>
+        <v>-79.52889251708984</v>
       </c>
       <c r="R26" t="n">
-        <v>-73.49773406982422</v>
+        <v>-62.25662994384766</v>
       </c>
       <c r="S26" t="n">
-        <v>-69.84254455566406</v>
+        <v>-68.69557952880859</v>
       </c>
       <c r="T26" t="n">
-        <v>-76.10858917236328</v>
+        <v>-77.48091125488281</v>
       </c>
       <c r="U26" t="n">
-        <v>-72.68955993652344</v>
+        <v>-66.19990539550781</v>
       </c>
       <c r="V26" t="n">
-        <v>-75.98991394042969</v>
+        <v>-48.44904327392578</v>
       </c>
       <c r="W26" t="n">
-        <v>-73.50067138671875</v>
+        <v>-65.27348327636719</v>
       </c>
       <c r="X26" t="n">
-        <v>-70.84888458251953</v>
+        <v>-71.82416534423828</v>
       </c>
       <c r="Y26" t="n">
-        <v>-78.12849426269531</v>
+        <v>-64.45857238769531</v>
       </c>
       <c r="Z26" t="n">
-        <v>-73.44528961181641</v>
+        <v>-65.63533020019531</v>
       </c>
       <c r="AA26" t="n">
-        <v>-70.856201171875</v>
+        <v>-50.72666168212891</v>
       </c>
       <c r="AB26" t="n">
-        <v>-71.34553527832031</v>
+        <v>-71.65486907958984</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>-64.22068786621094</v>
+        <v>-80.18943786621094</v>
       </c>
       <c r="B27" t="n">
-        <v>-63.43831253051758</v>
+        <v>-62.99501419067383</v>
       </c>
       <c r="C27" t="n">
-        <v>-66.33255767822266</v>
+        <v>-75.27136993408203</v>
       </c>
       <c r="D27" t="n">
-        <v>-63.56766891479492</v>
+        <v>-83.67688751220703</v>
       </c>
       <c r="E27" t="n">
-        <v>-65.24250793457031</v>
+        <v>-80.96230316162109</v>
       </c>
       <c r="F27" t="n">
-        <v>-62.76729583740234</v>
+        <v>-74.66845703125</v>
       </c>
       <c r="G27" t="n">
-        <v>-61.10712432861328</v>
+        <v>-79.55982971191406</v>
       </c>
       <c r="H27" t="n">
-        <v>-63.72469329833984</v>
+        <v>-70.43560028076172</v>
       </c>
       <c r="I27" t="n">
-        <v>-62.52690505981445</v>
+        <v>-83.84196472167969</v>
       </c>
       <c r="J27" t="n">
-        <v>-60.7172737121582</v>
+        <v>-66.19318389892578</v>
       </c>
       <c r="K27" t="n">
-        <v>-60.40779495239258</v>
+        <v>-83.4423828125</v>
       </c>
       <c r="L27" t="n">
-        <v>-65.91757965087891</v>
+        <v>-74.57945251464844</v>
       </c>
       <c r="M27" t="n">
-        <v>-61.01865386962891</v>
+        <v>-73.45359039306641</v>
       </c>
       <c r="N27" t="n">
-        <v>-63.81523895263672</v>
+        <v>-75.54022979736328</v>
       </c>
       <c r="O27" t="n">
-        <v>-76.33586120605469</v>
+        <v>-88.59324645996094</v>
       </c>
       <c r="P27" t="n">
-        <v>-73.61817932128906</v>
+        <v>-74.33363342285156</v>
       </c>
       <c r="Q27" t="n">
-        <v>-71.98040008544922</v>
+        <v>-82.42167663574219</v>
       </c>
       <c r="R27" t="n">
-        <v>-74.71797180175781</v>
+        <v>-73.07437133789062</v>
       </c>
       <c r="S27" t="n">
-        <v>-67.10956573486328</v>
+        <v>-78.68684387207031</v>
       </c>
       <c r="T27" t="n">
-        <v>-75.61988067626953</v>
+        <v>-75.38529205322266</v>
       </c>
       <c r="U27" t="n">
-        <v>-78.36502075195312</v>
+        <v>-90.06269073486328</v>
       </c>
       <c r="V27" t="n">
-        <v>-71.84078216552734</v>
+        <v>-78.21661376953125</v>
       </c>
       <c r="W27" t="n">
-        <v>-72.40296936035156</v>
+        <v>-80.15670013427734</v>
       </c>
       <c r="X27" t="n">
-        <v>-73.70793914794922</v>
+        <v>-75.78015899658203</v>
       </c>
       <c r="Y27" t="n">
-        <v>-76.37092590332031</v>
+        <v>-91.19271850585938</v>
       </c>
       <c r="Z27" t="n">
-        <v>-74.30497741699219</v>
+        <v>-82.19062805175781</v>
       </c>
       <c r="AA27" t="n">
-        <v>-71.51579284667969</v>
+        <v>-59.46192169189453</v>
       </c>
       <c r="AB27" t="n">
-        <v>-71.33209228515625</v>
+        <v>-70.01985168457031</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>-59.97118377685547</v>
+        <v>-76.42188262939453</v>
       </c>
       <c r="B28" t="n">
-        <v>-64.56478118896484</v>
+        <v>-75.98118591308594</v>
       </c>
       <c r="C28" t="n">
-        <v>-58.69533538818359</v>
+        <v>-88.13230895996094</v>
       </c>
       <c r="D28" t="n">
-        <v>-65.63258361816406</v>
+        <v>-60.30028533935547</v>
       </c>
       <c r="E28" t="n">
-        <v>-60.78047561645508</v>
+        <v>-80.04629516601562</v>
       </c>
       <c r="F28" t="n">
-        <v>-63.26719284057617</v>
+        <v>-57.32756423950195</v>
       </c>
       <c r="G28" t="n">
-        <v>-62.03495407104492</v>
+        <v>-79.50425720214844</v>
       </c>
       <c r="H28" t="n">
-        <v>-63.49372482299805</v>
+        <v>-53.5589714050293</v>
       </c>
       <c r="I28" t="n">
-        <v>-63.68904876708984</v>
+        <v>-67.63276672363281</v>
       </c>
       <c r="J28" t="n">
-        <v>-64.79737854003906</v>
+        <v>-63.45774459838867</v>
       </c>
       <c r="K28" t="n">
-        <v>-60.09431076049805</v>
+        <v>-84.45367431640625</v>
       </c>
       <c r="L28" t="n">
-        <v>-63.13777542114258</v>
+        <v>-79.78605651855469</v>
       </c>
       <c r="M28" t="n">
-        <v>-67.22761535644531</v>
+        <v>-70.82941436767578</v>
       </c>
       <c r="N28" t="n">
-        <v>-64.03511047363281</v>
+        <v>-54.44004440307617</v>
       </c>
       <c r="O28" t="n">
-        <v>-73.04212951660156</v>
+        <v>-85.73846435546875</v>
       </c>
       <c r="P28" t="n">
-        <v>-73.09429931640625</v>
+        <v>-66.08406829833984</v>
       </c>
       <c r="Q28" t="n">
-        <v>-71.56651306152344</v>
+        <v>-60.52587127685547</v>
       </c>
       <c r="R28" t="n">
-        <v>-73.13285827636719</v>
+        <v>-69.38308715820312</v>
       </c>
       <c r="S28" t="n">
-        <v>-69.94599914550781</v>
+        <v>-79.29801940917969</v>
       </c>
       <c r="T28" t="n">
-        <v>-72.47910308837891</v>
+        <v>-63.84697723388672</v>
       </c>
       <c r="U28" t="n">
-        <v>-76.80852508544922</v>
+        <v>-77.88983154296875</v>
       </c>
       <c r="V28" t="n">
-        <v>-76.61931610107422</v>
+        <v>-60.68101119995117</v>
       </c>
       <c r="W28" t="n">
-        <v>-70.93962097167969</v>
+        <v>-90.05527496337891</v>
       </c>
       <c r="X28" t="n">
-        <v>-73.12296295166016</v>
+        <v>-74.13523864746094</v>
       </c>
       <c r="Y28" t="n">
-        <v>-73.38505554199219</v>
+        <v>-87.52857208251953</v>
       </c>
       <c r="Z28" t="n">
-        <v>-75.21922302246094</v>
+        <v>-77.05252838134766</v>
       </c>
       <c r="AA28" t="n">
-        <v>-77.08155822753906</v>
+        <v>-70.95256805419922</v>
       </c>
       <c r="AB28" t="n">
-        <v>-75.67135620117188</v>
+        <v>-48.01715850830078</v>
       </c>
     </row>
   </sheetData>
